--- a/data/trans_orig/P16A10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>49265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440384</t>
+          <t>439819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460221</t>
+          <t>459590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285369</t>
+          <t>285667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300072</t>
+          <t>300665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731621</t>
+          <t>731192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756403</t>
+          <t>757140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343987</t>
+          <t>344902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359687</t>
+          <t>359641</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357668</t>
+          <t>356721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369520</t>
+          <t>369510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709100</t>
+          <t>708654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727156</t>
+          <t>727172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45937</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52425</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496452</t>
+          <t>497093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518389</t>
+          <t>518301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155799</t>
+          <t>155383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165731</t>
+          <t>165684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>658118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681638</t>
+          <t>682569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>72515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108645</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42633</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100236</t>
+          <t>98904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142843</t>
+          <t>141870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1129689</t>
+          <t>1130184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1163871</t>
+          <t>1165819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671652</t>
+          <t>672505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693885</t>
+          <t>694288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1809777</t>
+          <t>1810750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1852384</t>
+          <t>1853716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>48537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>40698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70049</t>
+          <t>69622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321762</t>
+          <t>321322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337543</t>
+          <t>337366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>518603</t>
+          <t>520215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543347</t>
+          <t>543287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848240</t>
+          <t>848667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877227</t>
+          <t>877591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>72202</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108322</t>
+          <t>108908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73051</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109512</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293800</t>
+          <t>293743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1140438</t>
+          <t>1139852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1177654</t>
+          <t>1176558</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1437448</t>
+          <t>1436751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1473909</t>
+          <t>1474846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152843</t>
+          <t>154459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205379</t>
+          <t>205429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152830</t>
+          <t>150846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206410</t>
+          <t>205855</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320922</t>
+          <t>320501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390019</t>
+          <t>391359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3063793</t>
+          <t>3063743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3116329</t>
+          <t>3114713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3171714</t>
+          <t>3172269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3225294</t>
+          <t>3227278</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6257277</t>
+          <t>6255937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6326374</t>
+          <t>6326795</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36865</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>38533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400346</t>
+          <t>401695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422061</t>
+          <t>421647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307347</t>
+          <t>307193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712110</t>
+          <t>713132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734598</t>
+          <t>734406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>28097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>29789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389991</t>
+          <t>388921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408180</t>
+          <t>407880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327163</t>
+          <t>327758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722620</t>
+          <t>724263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743275</t>
+          <t>744261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575228</t>
+          <t>575104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599593</t>
+          <t>599865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240508</t>
+          <t>240489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252804</t>
+          <t>253565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822040</t>
+          <t>821815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>849358</t>
+          <t>848343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>52646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,82 +4412,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21826</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32788</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>89536</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>72944</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>111098</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21826</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13876</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31930</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>89536</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>72191</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>111660</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1073795</t>
+          <t>1072879</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1104286</t>
+          <t>1105484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>744831</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>733869</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>752527</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1835252</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1813690</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1851844</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>95,35%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744831</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>734727</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>752781</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1835252</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1813128</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1852597</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80035</t>
+          <t>80622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>76511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113114</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467832</t>
+          <t>468652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489814</t>
+          <t>490763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680452</t>
+          <t>679865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710991</t>
+          <t>711360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1157970</t>
+          <t>1155818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1194103</t>
+          <t>1194573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54818</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88192</t>
+          <t>87956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58842</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>92796</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252539</t>
+          <t>251614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264817</t>
+          <t>263910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1017247</t>
+          <t>1017483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1050621</t>
+          <t>1049837</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1278629</t>
+          <t>1278484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1312438</t>
+          <t>1312663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>155126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208551</t>
+          <t>207819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144181</t>
+          <t>141850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195838</t>
+          <t>194399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311777</t>
+          <t>312392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>385645</t>
+          <t>385773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206583</t>
+          <t>3207315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3260477</t>
+          <t>3260008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3346172</t>
+          <t>3347611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3397829</t>
+          <t>3400160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6571499</t>
+          <t>6571371</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6645367</t>
+          <t>6644752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56066</t>
+          <t>56254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393870</t>
+          <t>393761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413490</t>
+          <t>414057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319649</t>
+          <t>319424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336473</t>
+          <t>337207</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>720081</t>
+          <t>719893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747351</t>
+          <t>746328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350298</t>
+          <t>348948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366293</t>
+          <t>365980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356494</t>
+          <t>356609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370030</t>
+          <t>370156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712040</t>
+          <t>712950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733275</t>
+          <t>733472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>49479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>32510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471672</t>
+          <t>472435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495923</t>
+          <t>495277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149544</t>
+          <t>148646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162601</t>
+          <t>162414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626744</t>
+          <t>629228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654518</t>
+          <t>655526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63401</t>
+          <t>65950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98165</t>
+          <t>100725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91718</t>
+          <t>91836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132205</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1051473</t>
+          <t>1048913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1086237</t>
+          <t>1083688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>783287</t>
+          <t>783683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>806223</t>
+          <t>806747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1843309</t>
+          <t>1841052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1883796</t>
+          <t>1883678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>33152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>56492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69196</t>
+          <t>67430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>103627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>564547</t>
+          <t>562857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>588821</t>
+          <t>587554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682305</t>
+          <t>681752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708935</t>
+          <t>707725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255026</t>
+          <t>1255323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289754</t>
+          <t>1291520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69607</t>
+          <t>69379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>109200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>68948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108482</t>
+          <t>108126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>973927</t>
+          <t>972825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1012418</t>
+          <t>1012646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1260688</t>
+          <t>1261044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1299499</t>
+          <t>1300222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177698</t>
+          <t>177088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>237627</t>
+          <t>230895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164193</t>
+          <t>162972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222622</t>
+          <t>222700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>356248</t>
+          <t>356596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>436725</t>
+          <t>431298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3148095</t>
+          <t>3154827</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208024</t>
+          <t>3208634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3308974</t>
+          <t>3308896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3367403</t>
+          <t>3368624</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6480593</t>
+          <t>6486020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6561070</t>
+          <t>6560722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471883</t>
+          <t>472633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488704</t>
+          <t>488979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430700</t>
+          <t>430609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440658</t>
+          <t>440839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906756</t>
+          <t>906356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>925921</t>
+          <t>926887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422000</t>
+          <t>422014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437239</t>
+          <t>437372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371477</t>
+          <t>371856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379207</t>
+          <t>379073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796783</t>
+          <t>796644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>814247</t>
+          <t>814052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52993</t>
+          <t>53719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65173</t>
+          <t>63595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615271</t>
+          <t>614545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658034</t>
+          <t>656857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146309</t>
+          <t>146846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160353</t>
+          <t>159986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>770002</t>
+          <t>771580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818836</t>
+          <t>818086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60551</t>
+          <t>59290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>89350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71098</t>
+          <t>70787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123221</t>
+          <t>125236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>944794</t>
+          <t>945469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>974268</t>
+          <t>975529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937765</t>
+          <t>936517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>963827</t>
+          <t>963799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889126</t>
+          <t>1887111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941249</t>
+          <t>1941560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>68876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69311</t>
+          <t>68624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>101335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435545</t>
+          <t>435223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453835</t>
+          <t>452998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>770089</t>
+          <t>769508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>798378</t>
+          <t>797320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1210021</t>
+          <t>1211098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243122</t>
+          <t>1243809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55269</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78022</t>
+          <t>78751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>54199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79267</t>
+          <t>80247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236731</t>
+          <t>236585</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>682130</t>
+          <t>681401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>704883</t>
+          <t>704855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>921392</t>
+          <t>920412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945540</t>
+          <t>946460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137407</t>
+          <t>139296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206729</t>
+          <t>205510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143902</t>
+          <t>144468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204265</t>
+          <t>203895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>307553</t>
+          <t>305640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>397936</t>
+          <t>398063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3168335</t>
+          <t>3169554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3237657</t>
+          <t>3235768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3368757</t>
+          <t>3369127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3429120</t>
+          <t>3428554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550150</t>
+          <t>6550023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6640533</t>
+          <t>6642446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>24061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49265</t>
+          <t>48943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439819</t>
+          <t>440556</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459590</t>
+          <t>459083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285667</t>
+          <t>285614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300665</t>
+          <t>300438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731192</t>
+          <t>731514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>757140</t>
+          <t>756396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>30831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344902</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359641</t>
+          <t>360479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356721</t>
+          <t>357743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369510</t>
+          <t>369469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708654</t>
+          <t>707968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727172</t>
+          <t>727019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>52269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497093</t>
+          <t>496951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518301</t>
+          <t>518298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155383</t>
+          <t>154946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165684</t>
+          <t>164969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658118</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682569</t>
+          <t>681220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72515</t>
+          <t>72896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108150</t>
+          <t>107518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141870</t>
+          <t>139598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130184</t>
+          <t>1130816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1165819</t>
+          <t>1165438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672505</t>
+          <t>672777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>693951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1810750</t>
+          <t>1813022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1853716</t>
+          <t>1854498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69622</t>
+          <t>71148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321322</t>
+          <t>321698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337366</t>
+          <t>338459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520215</t>
+          <t>519295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543287</t>
+          <t>543280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848667</t>
+          <t>847141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877591</t>
+          <t>875526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72202</t>
+          <t>71642</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108908</t>
+          <t>108825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72114</t>
+          <t>72478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110209</t>
+          <t>108663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293743</t>
+          <t>293538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1139852</t>
+          <t>1139935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1176558</t>
+          <t>1177118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1436751</t>
+          <t>1438297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1474846</t>
+          <t>1474482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154459</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205429</t>
+          <t>203921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150846</t>
+          <t>156653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205855</t>
+          <t>209153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320501</t>
+          <t>322344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391359</t>
+          <t>392761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3063743</t>
+          <t>3065251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3114713</t>
+          <t>3115788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3172269</t>
+          <t>3168971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3227278</t>
+          <t>3221471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6255937</t>
+          <t>6254535</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6326795</t>
+          <t>6324952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35516</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401695</t>
+          <t>400362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421647</t>
+          <t>421668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307193</t>
+          <t>306842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713132</t>
+          <t>713211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734406</t>
+          <t>734225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388921</t>
+          <t>390354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407880</t>
+          <t>408436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327758</t>
+          <t>327537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724263</t>
+          <t>722453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744261</t>
+          <t>743456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>50853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>63060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575104</t>
+          <t>575485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599865</t>
+          <t>599270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240489</t>
+          <t>239512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253565</t>
+          <t>253543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>821815</t>
+          <t>821216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>848343</t>
+          <t>849297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85251</t>
+          <t>84040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72944</t>
+          <t>71696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>108257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1072879</t>
+          <t>1074090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1105484</t>
+          <t>1105509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733869</t>
+          <t>734651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>752527</t>
+          <t>752880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813690</t>
+          <t>1816531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1851844</t>
+          <t>1853092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49127</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80622</t>
+          <t>79257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>74762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115266</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468652</t>
+          <t>468418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490763</t>
+          <t>489735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679865</t>
+          <t>681230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>711360</t>
+          <t>711983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1155818</t>
+          <t>1158651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1194573</t>
+          <t>1196322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>54411</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92796</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251614</t>
+          <t>252108</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263910</t>
+          <t>264754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1017483</t>
+          <t>1018605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1049837</t>
+          <t>1051028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1278484</t>
+          <t>1279487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1312663</t>
+          <t>1313081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155126</t>
+          <t>155917</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207819</t>
+          <t>211005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141850</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194399</t>
+          <t>193503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>312392</t>
+          <t>314701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>385773</t>
+          <t>389525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3207315</t>
+          <t>3204129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3260008</t>
+          <t>3259217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3347611</t>
+          <t>3348507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3400160</t>
+          <t>3397010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6571371</t>
+          <t>6567619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6644752</t>
+          <t>6642443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56254</t>
+          <t>57604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393761</t>
+          <t>392722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414057</t>
+          <t>413270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319424</t>
+          <t>320361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337207</t>
+          <t>336781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719893</t>
+          <t>718543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746328</t>
+          <t>745689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348948</t>
+          <t>350090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365980</t>
+          <t>366720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356609</t>
+          <t>358108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370156</t>
+          <t>370128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712950</t>
+          <t>712381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733472</t>
+          <t>733590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>49845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58808</t>
+          <t>60114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472435</t>
+          <t>472069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495277</t>
+          <t>496212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148646</t>
+          <t>149118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162414</t>
+          <t>162552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629228</t>
+          <t>627922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655526</t>
+          <t>654655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65950</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100725</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91836</t>
+          <t>91807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134462</t>
+          <t>134285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1048913</t>
+          <t>1049632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1083688</t>
+          <t>1085508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>783683</t>
+          <t>783259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>806747</t>
+          <t>805586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841052</t>
+          <t>1841229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1883678</t>
+          <t>1883707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57849</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56492</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67430</t>
+          <t>68827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>104032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>562857</t>
+          <t>563523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>587554</t>
+          <t>588492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>681752</t>
+          <t>682015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707725</t>
+          <t>708471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255323</t>
+          <t>1254918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1291520</t>
+          <t>1290123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109200</t>
+          <t>108015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68948</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108126</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>972825</t>
+          <t>974010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1012646</t>
+          <t>1014128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261044</t>
+          <t>1259623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1300222</t>
+          <t>1299935</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177088</t>
+          <t>176609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230895</t>
+          <t>232501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162972</t>
+          <t>164194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222700</t>
+          <t>223469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>356596</t>
+          <t>352398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431298</t>
+          <t>433987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3154827</t>
+          <t>3153221</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208634</t>
+          <t>3209113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3308896</t>
+          <t>3308127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3368624</t>
+          <t>3367402</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6486020</t>
+          <t>6483331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6560722</t>
+          <t>6564920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>39106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>32052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>481450</t>
+          <t>522055</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472633</t>
+          <t>511512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488979</t>
+          <t>529646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>436523</t>
+          <t>475801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430609</t>
+          <t>469180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440839</t>
+          <t>480354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>917972</t>
+          <t>997856</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906356</t>
+          <t>985722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>926887</t>
+          <t>1006977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>40481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>430429</t>
+          <t>459729</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422014</t>
+          <t>451822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437372</t>
+          <t>467173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>375970</t>
+          <t>416199</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371856</t>
+          <t>411131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379073</t>
+          <t>419423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,27 +9159,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>806399</t>
+          <t>875928</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796644</t>
+          <t>865874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>814052</t>
+          <t>883880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53719</t>
+          <t>44973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42151</t>
+          <t>46959</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>637464</t>
+          <t>437700</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614545</t>
+          <t>426639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656857</t>
+          <t>446148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>155560</t>
+          <t>174451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146846</t>
+          <t>162549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159986</t>
+          <t>179548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>793024</t>
+          <t>612150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>771580</t>
+          <t>598073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818086</t>
+          <t>623672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73706</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89350</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102068</t>
+          <t>109550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>92251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>128671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>961113</t>
+          <t>1053099</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>945469</t>
+          <t>1034734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>975529</t>
+          <t>1066455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>949165</t>
+          <t>829809</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936517</t>
+          <t>820363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>963799</t>
+          <t>837532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1910279</t>
+          <t>1882908</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1887111</t>
+          <t>1863787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941560</t>
+          <t>1900207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>74964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>84612</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68624</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101335</t>
+          <t>107341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445302</t>
+          <t>536674</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435223</t>
+          <t>526091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452998</t>
+          <t>544704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>782519</t>
+          <t>767020</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>769508</t>
+          <t>754452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>797320</t>
+          <t>776858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1227821</t>
+          <t>1303694</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1211098</t>
+          <t>1289051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243809</t>
+          <t>1316758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838384</t>
+          <t>829416</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838384</t>
+          <t>829416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838384</t>
+          <t>829416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312433</t>
+          <t>1396392</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312433</t>
+          <t>1396392</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312433</t>
+          <t>1396392</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78751</t>
+          <t>86454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>73435</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54199</t>
+          <t>59360</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80247</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239496</t>
+          <t>236203</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236585</t>
+          <t>233987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>694293</t>
+          <t>770584</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>681401</t>
+          <t>756539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>704855</t>
+          <t>783155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>933789</t>
+          <t>1006786</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>920412</t>
+          <t>992968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946460</t>
+          <t>1020861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>179810</t>
+          <t>196030</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139296</t>
+          <t>173872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205510</t>
+          <t>221295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>178992</t>
+          <t>198212</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144468</t>
+          <t>178967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203895</t>
+          <t>221692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>358802</t>
+          <t>394242</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>305640</t>
+          <t>360441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398063</t>
+          <t>427257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3195254</t>
+          <t>3245458</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3169554</t>
+          <t>3220193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3235768</t>
+          <t>3267616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3394030</t>
+          <t>3433863</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3369127</t>
+          <t>3410383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3428554</t>
+          <t>3453108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6589284</t>
+          <t>6679321</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550023</t>
+          <t>6646306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6642446</t>
+          <t>6713122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573022</t>
+          <t>3632075</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573022</t>
+          <t>3632075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573022</t>
+          <t>3632075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948086</t>
+          <t>7073563</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948086</t>
+          <t>7073563</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948086</t>
+          <t>7073563</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
